--- a/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-HUANCHACO.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-HUANCHACO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-112011</t>
+          <t>I-112015</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,17 +508,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-8.0326655</t>
+          <t>-8.0242201</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-79.0618761</t>
+          <t>-79.0645712</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Miguel Grau / Calle José Carlos Mariátegui</t>
+          <t>Avenida Miguel Grau / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-112015</t>
+          <t>I-288982</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-8.0242201</t>
+          <t>-8.0406688</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-79.0645712</t>
+          <t>-79.0592911</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Miguel Grau</t>
+          <t>Avenida Miguel Grau / Calle Cápac Yupanqui</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-112016</t>
+          <t>I-42873</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,17 +612,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-8.0246215</t>
+          <t>-8.0174155</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-79.0644435</t>
+          <t>-79.0667816</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Miguel Grau / Calle Ramon Castilla</t>
+          <t>Avenida Miguel Grau / Calle José Galvez</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-112017</t>
+          <t>I-44591</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,17 +664,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-8.0326105</t>
+          <t>-8.0422088</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-79.0618874</t>
+          <t>-79.0585724</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Miguel Grau</t>
+          <t>Calle San Francisco / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-112018</t>
+          <t>I-509789</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-8.0319159</t>
+          <t>-8.081576</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-79.0620929</t>
+          <t>-79.1160391</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Miguel Grau</t>
+          <t>Avenida Juan Pablo II / Jirón Libertad</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-288982</t>
+          <t>I-112018</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-8.0406688</t>
+          <t>-8.0319159</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-79.0592911</t>
+          <t>-79.0620929</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida Miguel Grau / Calle Cápac Yupanqui</t>
+          <t>Avenida Miguel Grau / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-289347</t>
+          <t>I-704781</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -820,22 +820,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-8.0419089</t>
+          <t>-8.0256699</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-79.0589114</t>
+          <t>-79.0480115</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida Miguel Grau / Avenida Pachacútec</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>l-291540</t>
+          <t>I-436149</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -872,22 +872,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-8.0718011</t>
+          <t>-8.0972099</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-79.1136787</t>
+          <t>-79.0694793</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida Cerrito de la Virgen</t>
+          <t>Avenida Chan Chan / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>l-39768</t>
+          <t>I-585441</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -924,22 +924,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-8.0177196</t>
+          <t>-8.0697088</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-79.066681</t>
+          <t>-79.1173795</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida Miguel Grau / Calle Cesar Vallejo</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -951,7 +951,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>l-39985</t>
+          <t>I-576916</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -976,22 +976,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-8.0405215</t>
+          <t>-8.1074325</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-79.0593414</t>
+          <t>-79.0989326</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Avenida Independencia / Avenida Miguel Grau</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>l-42873</t>
+          <t>I-585434</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1028,22 +1028,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-8.0174155</t>
+          <t>-8.0695695</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-79.0667816</t>
+          <t>-79.1138001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Avenida Miguel Grau / Calle José Galvez</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>l-436148</t>
+          <t>I-6573</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1080,22 +1080,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-8.0974189</t>
+          <t>-8.0812114</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-79.0692977</t>
+          <t>-79.1226291</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida Chan Chan</t>
+          <t>Avenida la Rivera / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1107,7 +1107,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>l-436149</t>
+          <t>I-585459</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1132,22 +1132,22 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-8.0972099</t>
+          <t>-8.0710474</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-79.0694793</t>
+          <t>-79.098427</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Avenida Chan Chan</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>l-436170</t>
+          <t>I-585460</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-8.0881171</t>
+          <t>-8.0685727</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-79.093799</t>
+          <t>-79.0999844</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Avenida Ramón Castilla</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>l-436171</t>
+          <t>I-585461</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1236,22 +1236,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-8.087997</t>
+          <t>-8.0791231</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-79.0941732</t>
+          <t>-79.1057226</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Avenida Ramón Castilla</t>
+          <t>Avenida Circunvalación / Calle s / n</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>l-436180</t>
+          <t>I-585462</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1288,22 +1288,22 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-8.0974713</t>
+          <t>-8.0828282</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-79.069358</t>
+          <t>-79.1072271</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Avenida Chan Chan</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>l-436181</t>
+          <t>I-585463</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1340,22 +1340,22 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-8.0972747</t>
+          <t>-8.0737372</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-79.0695464</t>
+          <t>-79.0954894</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Avenida Chan Chan</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>l-44591</t>
+          <t>I-585464</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1392,22 +1392,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-8.0422088</t>
+          <t>-8.0726381</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-79.0585724</t>
+          <t>-79.0965736</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Calle San Francisco</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>l-44592</t>
+          <t>I-585466</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1444,493 +1444,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-8.0422399</t>
+          <t>-8.0667027</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-79.0588091</t>
+          <t>-79.0981454</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Avenida Miguel Grau / Calle San Francisco</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>l-493457</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-8.0815677</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-79.1163724</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Jr. Libertad / Pasaje Córdova</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>l-493472</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-8.0814029</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-79.1163459</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Pasaje Córdova</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>l-509789</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-8.081576</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-79.1160391</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Avenida Juan Pablo II / Jr. Libertad</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>l-585457</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-8.0717079</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-79.1137893</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>l-704781</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-8.0256699</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-79.0480115</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>l-7210</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-8.0975143</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-79.0696087</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>l-791110</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-8.041676</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-79.0589773</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Avenida Miguel Grau</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>l-805792</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-8.0815794</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-79.1159272</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Avenida Juan Pablo II</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>l-806103</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-8.0815729</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-79.1162194</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Jr. Libertad</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
         <is>
           <t>130104</t>
         </is>

--- a/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-HUANCHACO.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-HUANCHACO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1468,6 +1468,214 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>I-585440</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-8.0742923</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-79.1115188</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>130104</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>I-585444</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-8.0693916</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-79.1182727</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>130104</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>I-585446</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-8.0654986</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-79.1172432</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Avenida Ejército / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>130104</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I-585447</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-8.0639923</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-79.1149477</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>130104</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-HUANCHACO.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-HUANCHACO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Miguel Grau / Calle s / n</t>
+          <t>Avenida Miguel Grau / Calle Jorge Chavez</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Miguel Grau / Calle Cápac Yupanqui</t>
+          <t>Avenida Independencia / Avenida Miguel Grau / Calle Cápac Yupanqui</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida la Rivera / Calle s / n</t>
+          <t>Avenida la Rivera / Malecón Grau</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1671,6 +1671,214 @@
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>130104</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>I-585454</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-8.0704208</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-79.1143904</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>130104</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>I-585456</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-8.0704685</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-79.1154456</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>130104</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>I-585467</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-8.0634243</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-79.1187169</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>130104</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>I-585468</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-8.0634205</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-79.1190956</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>130104</t>
         </is>

--- a/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-HUANCHACO.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-HUANCHACO.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-112015</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-8.0242201</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-288982</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-8.0406688</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-42873</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-8.0174155</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-44591</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-8.0422088</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-509789</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-8.081576</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-112018</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-8.0319159</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-704781</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-8.0256699</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-436149</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-8.0972099</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-585441</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-8.0697088</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-576916</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-8.1074325</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-585434</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-8.0695695</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-6573</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-8.0812114</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-585459</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-8.0710474</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-585460</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-8.0685727</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-585461</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-8.0791231</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-585462</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-8.0828282</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-585463</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-8.0737372</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-585464</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-8.0726381</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-585466</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-8.0667027</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-585440</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-8.0742923</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-585444</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-8.0693916</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-585446</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-8.0654986</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-585447</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-8.0639923</t>
@@ -1668,40 +1553,35 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>I-585454</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-8.0704208</t>
@@ -1720,40 +1600,35 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>I-585456</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-8.0704685</t>
@@ -1772,40 +1647,35 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>I-585467</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-8.0634243</t>
@@ -1824,40 +1694,35 @@
       <c r="I27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>130104</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>HUANCHACO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>I-585468</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>130104</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>HUANCHACO</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-8.0634205</t>
@@ -1876,11 +1741,6 @@
       <c r="I28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>130104</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-HUANCHACO.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-HUANCHACO.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-HUANCHACO.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-HUANCHACO.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">

--- a/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-HUANCHACO.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-HUANCHACO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-HUANCHACO.xlsx
+++ b/Intersecciones/excels/LA_LIBERTAD-TRUJILLO-HUANCHACO.xlsx
@@ -486,22 +486,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-112015</t>
+          <t>I-704781</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-8.0242201</t>
+          <t>-8.0256699</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-79.0645712</t>
+          <t>-79.0480115</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Miguel Grau / Calle Jorge Chavez</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -533,27 +533,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-288982</t>
+          <t>I-6573</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-8.0406688</t>
+          <t>-8.0812114</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-79.0592911</t>
+          <t>-79.1226291</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Independencia / Avenida Miguel Grau / Calle Cápac Yupanqui</t>
+          <t>Avenida la Rivera / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -580,27 +580,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-42873</t>
+          <t>I-585468</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-8.0174155</t>
+          <t>-8.0634205</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-79.0667816</t>
+          <t>-79.1190956</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Miguel Grau / Calle José Galvez</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -627,27 +627,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-44591</t>
+          <t>I-585467</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-8.0422088</t>
+          <t>-8.0634243</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-79.0585724</t>
+          <t>-79.1187169</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Calle San Francisco / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -674,27 +674,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-509789</t>
+          <t>I-585466</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-8.081576</t>
+          <t>-8.0667027</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-79.1160391</t>
+          <t>-79.0981454</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Juan Pablo II / Jirón Libertad</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -721,27 +721,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-112018</t>
+          <t>I-585464</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-8.0319159</t>
+          <t>-8.0726381</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-79.0620929</t>
+          <t>-79.0965736</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida Miguel Grau / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -768,17 +768,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-704781</t>
+          <t>I-585463</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-8.0256699</t>
+          <t>-8.0737372</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-79.0480115</t>
+          <t>-79.0954894</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -815,27 +815,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-436149</t>
+          <t>I-585462</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-8.0972099</t>
+          <t>-8.0828282</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-79.0694793</t>
+          <t>-79.1072271</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida Chan Chan / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -862,22 +862,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-585441</t>
+          <t>I-585461</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-8.0697088</t>
+          <t>-8.0791231</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-79.1173795</t>
+          <t>-79.1057226</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Circunvalación / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -909,17 +909,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-576916</t>
+          <t>I-585460</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-8.1074325</t>
+          <t>-8.0685727</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-79.0989326</t>
+          <t>-79.0999844</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-585434</t>
+          <t>I-585459</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-8.0695695</t>
+          <t>-8.0710474</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-79.1138001</t>
+          <t>-79.098427</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1003,22 +1003,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-6573</t>
+          <t>I-585456</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-8.0812114</t>
+          <t>-8.0704685</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-79.1226291</t>
+          <t>-79.1154456</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida la Rivera / Malecón Grau</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1050,17 +1050,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-585459</t>
+          <t>I-585454</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-8.0710474</t>
+          <t>-8.0704208</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-79.098427</t>
+          <t>-79.1143904</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-585460</t>
+          <t>I-585447</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-8.0685727</t>
+          <t>-8.0639923</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-79.0999844</t>
+          <t>-79.1149477</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-585461</t>
+          <t>I-585446</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-8.0791231</t>
+          <t>-8.0654986</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-79.1057226</t>
+          <t>-79.1172432</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Avenida Circunvalación / Calle s / n</t>
+          <t>Avenida Ejército / Calle s / n</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-585462</t>
+          <t>I-585444</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-8.0828282</t>
+          <t>-8.0693916</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-79.1072271</t>
+          <t>-79.1182727</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-585463</t>
+          <t>I-585441</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-8.0737372</t>
+          <t>-8.0697088</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-79.0954894</t>
+          <t>-79.1173795</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-585464</t>
+          <t>I-585440</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-8.0726381</t>
+          <t>-8.0742923</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-79.0965736</t>
+          <t>-79.1115188</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1332,17 +1332,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-585466</t>
+          <t>I-585434</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-8.0667027</t>
+          <t>-8.0695695</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-79.0981454</t>
+          <t>-79.1138001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1379,17 +1379,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-585440</t>
+          <t>I-576916</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-8.0742923</t>
+          <t>-8.1074325</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-79.1115188</t>
+          <t>-79.0989326</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1426,27 +1426,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-585444</t>
+          <t>I-509789</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-8.0693916</t>
+          <t>-8.081576</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-79.1182727</t>
+          <t>-79.1160391</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Juan Pablo II / Jirón Libertad</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1473,27 +1473,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-585446</t>
+          <t>I-44591</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-8.0654986</t>
+          <t>-8.0422088</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-79.1172432</t>
+          <t>-79.0585724</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Avenida Ejército / Calle s / n</t>
+          <t>Calle San Francisco / Calle s / n</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1520,27 +1520,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-585447</t>
+          <t>I-436149</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-8.0639923</t>
+          <t>-8.0972099</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-79.1149477</t>
+          <t>-79.0694793</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Chan Chan / Calle s / n</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-585454</t>
+          <t>I-42873</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-8.0704208</t>
+          <t>-8.0174155</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-79.1143904</t>
+          <t>-79.0667816</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Miguel Grau / Calle José Galvez</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1614,27 +1614,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-585456</t>
+          <t>I-288982</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-8.0704685</t>
+          <t>-8.0406688</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-79.1154456</t>
+          <t>-79.0592911</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Miguel Grau / Calle Cápac Yupanqui</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1661,27 +1661,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I-585467</t>
+          <t>I-112018</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-8.0634243</t>
+          <t>-8.0319159</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-79.1187169</t>
+          <t>-79.0620929</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Miguel Grau / Calle s / n</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1708,27 +1708,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I-585468</t>
+          <t>I-112015</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-8.0634205</t>
+          <t>-8.0242201</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-79.1190956</t>
+          <t>-79.0645712</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Miguel Grau / Calle s / n</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
